--- a/downloads/other-states.xlsx
+++ b/downloads/other-states.xlsx
@@ -15547,7 +15547,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>region</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -34551,7 +34551,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -34701,7 +34701,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>

--- a/downloads/other-states.xlsx
+++ b/downloads/other-states.xlsx
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -17925,33 +17925,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>districts_press</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ludhiana</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>416000</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20100727</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>The Tribune, the draft roll by district</t>
+          <t>ANI, the Chief Electoral Officer's release with the final roll</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -17960,33 +17955,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>districts_press</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Amritsar</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>242000</v>
+          <t>men_final</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10376026</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>The Tribune, the draft roll by district</t>
+          <t>ANI, the Chief Electoral Officer's release with the final roll</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -17995,33 +17985,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>districts_press</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jalandhar</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>184000</v>
+          <t>women_final</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9724195</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>The Tribune, the draft roll by district</t>
+          <t>ANI, the Chief Electoral Officer's release with the final roll</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -18030,33 +18015,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>districts_press</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAS Nagar (Mohali)</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>153000</v>
+          <t>third_final</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>506</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>The Tribune, the draft roll by district</t>
+          <t>ANI, the Chief Electoral Officer's release with the final roll</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -18065,33 +18045,323 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>added_after</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>797263</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ANI, the Chief Electoral Officer's release with the final roll</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>notices</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3549036</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>The Hindu, the Chief Electoral Officer's statement with the final roll</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>men_before</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11176866</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>The Hindu, the Chief Electoral Officer's statement with the final roll</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>women_before</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10283478</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>The Hindu, the Chief Electoral Officer's statement with the final roll</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>third_before</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>699</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>The Hindu, the Chief Electoral Officer's statement with the final roll</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>districts_press</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>district</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>416000</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>The Tribune, the draft roll by district</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>districts_press</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>242000</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>The Tribune, the draft roll by district</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>districts_press</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>184000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>The Tribune, the draft roll by district</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>districts_press</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SAS Nagar (Mohali)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>153000</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>The Tribune, the draft roll by district</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>districts_press</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>district</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Patiala</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G20" t="n">
         <v>138000</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>The Tribune, the draft roll by district</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/downloads/other-states.xlsx
+++ b/downloads/other-states.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>How many names were left off in any ward or sector. The Chief Electoral Officer's site could not be reached and no table below the union territory was found. A ward table that newspapers reported from a chart shared by the member of parliament. It compares the roll of the 2024 Lok Sabha election with a later roll, two years apart, and gives a percentage for most wards and a count for only six, for 17 of the 35 wards. The chart's own date is reported as 2 August 2026 and the chart itself was not found, so it is left out. The draft by sex and the names left off by sex. They were reported in one news agency story that could not be read, so they are left out. How many of the 15,117 names added after the draft were people left off it.</t>
+          <t>How many names were left off in any ward or sector. No table below the union territory was found. A ward table that newspapers reported from a chart shared by the member of parliament. It compares the roll of the 2024 Lok Sabha election with a later roll, two years apart, and gives a percentage for most wards and a count for only six, for 17 of the 35 wards. The chart's own date is reported as 2 August 2026 and the chart itself was not found, so it is left out. The draft by sex and the names left off by sex. They were reported in one news agency story whose text is not available, so they are left out. How many of the 15,117 names added after the draft were people left off it.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>There are no figures yet. The roll before the revision, the names left off and their reasons will be known only when the draft is published. The Chief Electoral Officer's site could not be reached, so nothing was read from it.</t>
+          <t>There are no figures yet. The roll before the revision, the names left off and their reasons will be known only when the draft is published.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">

--- a/downloads/other-states.xlsx
+++ b/downloads/other-states.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>The roll before or the draft for each district or tehsil. Only the names left off were reported by district, and only the final roll was published by tehsil. The reasons for the names left off in any district or tehsil. Women's share of the names left off. The roll before was not published by sex. How many electors were removed after a notice. The final statement counts them together with those removed for shifting.</t>
+          <t>The roll before or the draft for each district or tehsil. Only the names left off were reported by district, and only the final roll was published by tehsil. The reasons for the names left off in any district or tehsil. Women's share of the names left off. The roll before was not published by sex. How many electors were deleted after a notice. The final statement counts them together with those deleted for shifting.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>The reasons as exact counts, or by district or by sex. The Chief Electoral Officer published them for the state only, in lakh. The names left off in each constituency. No constituency table was found. The final roll and the names added and removed after the draft, which had not been published when these figures were collected.</t>
+          <t>The reasons as exact counts, or by district or by sex. The Chief Electoral Officer published them for the state only, in lakh. The names left off in each constituency. No constituency table was found. The final roll and the names added and deleted after the draft, which had not been published when these figures were collected.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Any figure for 1-Daman and Diu on its own. No document of its registration officer was found. The roll, the draft or the final roll for each of the three districts. Counts of the reasons for the territory as a whole. They were reported only as shares. How many names were added and how many removed after the draft, or how many electors were sent a notice. Women's share of the names left off. The roll before and the draft were not found by sex.</t>
+          <t>Any figure for 1-Daman and Diu on its own. No document of its registration officer was found. The roll, the draft or the final roll for each of the three districts. Counts of the reasons for the territory as a whole. They were reported only as shares. How many names were added and how many deleted after the draft, or how many electors were sent a notice. Women's share of the names left off. The roll before and the draft were not found by sex.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -30076,7 +30076,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -30722,7 +30722,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -31045,7 +31045,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice).</t>
+          <t>Which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice).</t>
         </is>
       </c>
     </row>
@@ -31113,7 +31113,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -31368,7 +31368,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -31436,7 +31436,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>On table rows, on an after table row, names removed after the draft, as a count.</t>
+          <t>On table rows, on an after table row, names deleted after the draft, as a count.</t>
         </is>
       </c>
     </row>
@@ -31470,7 +31470,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>On table rows, names added less names removed after the draft, a net change that counts new voters as well as names put back, as a count.</t>
+          <t>On table rows, names added less names deleted after the draft, a net change that counts new voters as well as names put back, as a count.</t>
         </is>
       </c>
     </row>
@@ -31759,7 +31759,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32014,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_removed means men left off the draft, women_removed means women left off the draft, third_removed means third-gender electors left off the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_removed means men left off the draft, women_removed means women left off the draft, third_removed means third-gender electors left off the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -32728,7 +32728,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -32983,7 +32983,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -33629,7 +33629,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_removed means men left off the draft, women_removed means women left off the draft, third_removed means third-gender electors left off the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_removed means men left off the draft, women_removed means women left off the draft, third_removed means third-gender electors left off the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -33697,7 +33697,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -34275,7 +34275,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -34343,7 +34343,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -34666,7 +34666,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -34921,7 +34921,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -35244,7 +35244,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
+          <t>For a state row, which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll), and for a table row the name of the area it describes.</t>
         </is>
       </c>
     </row>
@@ -35312,7 +35312,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -35890,7 +35890,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names removed after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice).</t>
+          <t>Which headline figure the value is (roll_before means the roll before the revision, draft means the draft roll, removed means the names left off the draft, dead means names left off entered as dead, shifted_absent_other means names left off entered as shifted, absent or other, duplicate means names left off entered as enrolled more than once, added_after means names added after the draft, removed_after means names deleted after the draft, net_after means the net change after the draft, final means the final roll, men_before means men on the roll before, women_before means women on the roll before, third_before means third-gender electors on the roll before, men_draft means men on the draft, women_draft means women on the draft, third_draft means third-gender electors on the draft, men_final means men on the final roll, women_final means women on the final roll, third_final means third-gender electors on the final roll, notices means electors kept on the draft but sent a notice).</t>
         </is>
       </c>
     </row>
@@ -35958,7 +35958,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>On table rows, names left off the draft in an area, or names removed after the draft in an after table, as a count, and it is blank in every row of this file.</t>
+          <t>On table rows, names left off the draft in an area, or names deleted after the draft in an after table, as a count, and it is blank in every row of this file.</t>
         </is>
       </c>
     </row>
@@ -36281,7 +36281,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Empty in this file because Tripura has published no draft roll yet, and once it does it will hold names left off the draft, or removed after it, in an area.</t>
+          <t>Empty in this file because Tripura has published no draft roll yet, and once it does it will hold names left off the draft, or deleted after it, in an area.</t>
         </is>
       </c>
     </row>

--- a/downloads/other-states.xlsx
+++ b/downloads/other-states.xlsx
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Women's share of the names left off in any district or constituency. The roll by sex was published for the state only. Where the notices and hearings fell. They were published as state totals only. The final roll, which was not out when these figures were read.</t>
+          <t>Women's share of the names left off in any district or constituency. The roll by sex was published for the state only. Where the notices and hearings fell, and where names were added or deleted after the draft. They were published as state totals only. The final roll by district or constituency. The note of 26 October 2026 gives it for the state only, so the district and constituency figures stop at the draft. How many of the 21,694 electors added on Form 6 or 6A had been left off the draft and how many were new voters.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -8232,7 +8232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S89"/>
+  <dimension ref="A1:S96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8816,15 +8816,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>notices</t>
+          <t>added_after</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>651735</v>
+        <v>23970</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/87 of 1 October 2026</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -8836,48 +8836,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>West Jaintia Hills</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>220478</v>
-      </c>
-      <c r="F18" t="n">
-        <v>209908</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10570</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7097</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3151</v>
-      </c>
-      <c r="P18" t="n">
-        <v>322</v>
+          <t>removed_after</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>9250</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8886,48 +8866,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ri-Bhoi</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>205735</v>
-      </c>
-      <c r="F19" t="n">
-        <v>190066</v>
-      </c>
-      <c r="G19" t="n">
-        <v>15669</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6096</v>
-      </c>
-      <c r="O19" t="n">
-        <v>9040</v>
-      </c>
-      <c r="P19" t="n">
-        <v>533</v>
+          <t>net_after</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14720</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8936,48 +8896,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>East Khasi Hills</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>632146</v>
-      </c>
-      <c r="F20" t="n">
-        <v>562160</v>
-      </c>
-      <c r="G20" t="n">
-        <v>69986</v>
-      </c>
-      <c r="N20" t="n">
-        <v>27319</v>
-      </c>
-      <c r="O20" t="n">
-        <v>40940</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1727</v>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2183963</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -8986,48 +8926,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>West Khasi Hills</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>137727</v>
-      </c>
-      <c r="F21" t="n">
-        <v>129820</v>
-      </c>
-      <c r="G21" t="n">
-        <v>7907</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4455</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3013</v>
-      </c>
-      <c r="P21" t="n">
-        <v>439</v>
+          <t>men_final</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1059743</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9036,48 +8956,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>East Garo Hills</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>114767</v>
-      </c>
-      <c r="F22" t="n">
-        <v>105512</v>
-      </c>
-      <c r="G22" t="n">
-        <v>9255</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2905</v>
-      </c>
-      <c r="O22" t="n">
-        <v>5761</v>
-      </c>
-      <c r="P22" t="n">
-        <v>589</v>
+          <t>women_final</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1124216</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9086,48 +8986,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>West Garo Hills</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>396914</v>
-      </c>
-      <c r="F23" t="n">
-        <v>367382</v>
-      </c>
-      <c r="G23" t="n">
-        <v>29532</v>
-      </c>
-      <c r="N23" t="n">
-        <v>15613</v>
-      </c>
-      <c r="O23" t="n">
-        <v>12874</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1045</v>
+          <t>third_final</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9136,48 +9016,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>districts</t>
+          <t>state</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>district</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Garo Hills</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>110488</v>
-      </c>
-      <c r="F24" t="n">
-        <v>102649</v>
-      </c>
-      <c r="G24" t="n">
-        <v>7839</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3583</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3782</v>
-      </c>
-      <c r="P24" t="n">
-        <v>474</v>
+          <t>notices</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>651735</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/102 of 26 October 2026 on the final roll</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -9196,26 +9056,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>East Jaintia Hills</t>
+          <t>West Jaintia Hills</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>104417</v>
+        <v>220478</v>
       </c>
       <c r="F25" t="n">
-        <v>96791</v>
+        <v>209908</v>
       </c>
       <c r="G25" t="n">
-        <v>7626</v>
+        <v>10570</v>
       </c>
       <c r="N25" t="n">
-        <v>3598</v>
+        <v>7097</v>
       </c>
       <c r="O25" t="n">
-        <v>3448</v>
+        <v>3151</v>
       </c>
       <c r="P25" t="n">
-        <v>580</v>
+        <v>322</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -9246,26 +9106,26 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South West Khasi Hills</t>
+          <t>Ri-Bhoi</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>80592</v>
+        <v>205735</v>
       </c>
       <c r="F26" t="n">
-        <v>77124</v>
+        <v>190066</v>
       </c>
       <c r="G26" t="n">
-        <v>3468</v>
+        <v>15669</v>
       </c>
       <c r="N26" t="n">
-        <v>2305</v>
+        <v>6096</v>
       </c>
       <c r="O26" t="n">
-        <v>1017</v>
+        <v>9040</v>
       </c>
       <c r="P26" t="n">
-        <v>146</v>
+        <v>533</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -9296,26 +9156,26 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>North Garo Hills</t>
+          <t>East Khasi Hills</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>143748</v>
+        <v>632146</v>
       </c>
       <c r="F27" t="n">
-        <v>132013</v>
+        <v>562160</v>
       </c>
       <c r="G27" t="n">
-        <v>11735</v>
+        <v>69986</v>
       </c>
       <c r="N27" t="n">
-        <v>4578</v>
+        <v>27319</v>
       </c>
       <c r="O27" t="n">
-        <v>6769</v>
+        <v>40940</v>
       </c>
       <c r="P27" t="n">
-        <v>388</v>
+        <v>1727</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -9346,26 +9206,26 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South West Garo Hills</t>
+          <t>West Khasi Hills</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>108883</v>
+        <v>137727</v>
       </c>
       <c r="F28" t="n">
-        <v>104671</v>
+        <v>129820</v>
       </c>
       <c r="G28" t="n">
-        <v>4212</v>
+        <v>7907</v>
       </c>
       <c r="N28" t="n">
-        <v>2478</v>
+        <v>4455</v>
       </c>
       <c r="O28" t="n">
-        <v>1428</v>
+        <v>3013</v>
       </c>
       <c r="P28" t="n">
-        <v>306</v>
+        <v>439</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -9396,26 +9256,26 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eastern West Khasi Hills</t>
+          <t>East Garo Hills</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>93750</v>
+        <v>114767</v>
       </c>
       <c r="F29" t="n">
-        <v>91147</v>
+        <v>105512</v>
       </c>
       <c r="G29" t="n">
-        <v>2603</v>
+        <v>9255</v>
       </c>
       <c r="N29" t="n">
-        <v>1463</v>
+        <v>2905</v>
       </c>
       <c r="O29" t="n">
-        <v>988</v>
+        <v>5761</v>
       </c>
       <c r="P29" t="n">
-        <v>152</v>
+        <v>589</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -9436,36 +9296,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1 Nartiang</t>
+          <t>West Garo Hills</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>48718</v>
+        <v>396914</v>
       </c>
       <c r="F30" t="n">
-        <v>46104</v>
+        <v>367382</v>
       </c>
       <c r="G30" t="n">
-        <v>2614</v>
+        <v>29532</v>
       </c>
       <c r="N30" t="n">
-        <v>1807</v>
+        <v>15613</v>
       </c>
       <c r="O30" t="n">
-        <v>722</v>
+        <v>12874</v>
       </c>
       <c r="P30" t="n">
-        <v>85</v>
+        <v>1045</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -9486,36 +9346,36 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2 Jowai</t>
+          <t>South Garo Hills</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>43838</v>
+        <v>110488</v>
       </c>
       <c r="F31" t="n">
-        <v>41521</v>
+        <v>102649</v>
       </c>
       <c r="G31" t="n">
-        <v>2317</v>
+        <v>7839</v>
       </c>
       <c r="N31" t="n">
-        <v>1437</v>
+        <v>3583</v>
       </c>
       <c r="O31" t="n">
-        <v>795</v>
+        <v>3782</v>
       </c>
       <c r="P31" t="n">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -9536,36 +9396,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3 Raliang</t>
+          <t>East Jaintia Hills</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>42961</v>
+        <v>104417</v>
       </c>
       <c r="F32" t="n">
-        <v>40927</v>
+        <v>96791</v>
       </c>
       <c r="G32" t="n">
-        <v>2034</v>
+        <v>7626</v>
       </c>
       <c r="N32" t="n">
-        <v>1635</v>
+        <v>3598</v>
       </c>
       <c r="O32" t="n">
-        <v>361</v>
+        <v>3448</v>
       </c>
       <c r="P32" t="n">
-        <v>38</v>
+        <v>580</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -9586,36 +9446,36 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4 Mowkaiaw</t>
+          <t>South West Khasi Hills</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>42837</v>
+        <v>80592</v>
       </c>
       <c r="F33" t="n">
-        <v>40706</v>
+        <v>77124</v>
       </c>
       <c r="G33" t="n">
-        <v>2131</v>
+        <v>3468</v>
       </c>
       <c r="N33" t="n">
-        <v>1260</v>
+        <v>2305</v>
       </c>
       <c r="O33" t="n">
-        <v>774</v>
+        <v>1017</v>
       </c>
       <c r="P33" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -9636,36 +9496,36 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5 Sutnga Saipung</t>
+          <t>North Garo Hills</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>51956</v>
+        <v>143748</v>
       </c>
       <c r="F34" t="n">
-        <v>48631</v>
+        <v>132013</v>
       </c>
       <c r="G34" t="n">
-        <v>3325</v>
+        <v>11735</v>
       </c>
       <c r="N34" t="n">
-        <v>1614</v>
+        <v>4578</v>
       </c>
       <c r="O34" t="n">
-        <v>1390</v>
+        <v>6769</v>
       </c>
       <c r="P34" t="n">
-        <v>321</v>
+        <v>388</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -9686,36 +9546,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6 Khliehriat</t>
+          <t>South West Garo Hills</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>52461</v>
+        <v>108883</v>
       </c>
       <c r="F35" t="n">
-        <v>48160</v>
+        <v>104671</v>
       </c>
       <c r="G35" t="n">
-        <v>4301</v>
+        <v>4212</v>
       </c>
       <c r="N35" t="n">
-        <v>1984</v>
+        <v>2478</v>
       </c>
       <c r="O35" t="n">
-        <v>2058</v>
+        <v>1428</v>
       </c>
       <c r="P35" t="n">
-        <v>259</v>
+        <v>306</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -9736,36 +9596,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>constituencies</t>
+          <t>districts</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ac</t>
+          <t>district</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7 Amlarem</t>
+          <t>Eastern West Khasi Hills</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42124</v>
+        <v>93750</v>
       </c>
       <c r="F36" t="n">
-        <v>40650</v>
+        <v>91147</v>
       </c>
       <c r="G36" t="n">
-        <v>1474</v>
+        <v>2603</v>
       </c>
       <c r="N36" t="n">
-        <v>958</v>
+        <v>1463</v>
       </c>
       <c r="O36" t="n">
-        <v>499</v>
+        <v>988</v>
       </c>
       <c r="P36" t="n">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -9796,26 +9656,26 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8 Mawhati</t>
+          <t>1 Nartiang</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>42861</v>
+        <v>48718</v>
       </c>
       <c r="F37" t="n">
-        <v>40960</v>
+        <v>46104</v>
       </c>
       <c r="G37" t="n">
-        <v>1901</v>
+        <v>2614</v>
       </c>
       <c r="N37" t="n">
-        <v>1027</v>
+        <v>1807</v>
       </c>
       <c r="O37" t="n">
-        <v>793</v>
+        <v>722</v>
       </c>
       <c r="P37" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -9846,26 +9706,26 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9 Nongpoh</t>
+          <t>2 Jowai</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>40943</v>
+        <v>43838</v>
       </c>
       <c r="F38" t="n">
-        <v>38528</v>
+        <v>41521</v>
       </c>
       <c r="G38" t="n">
-        <v>2415</v>
+        <v>2317</v>
       </c>
       <c r="N38" t="n">
-        <v>1104</v>
+        <v>1437</v>
       </c>
       <c r="O38" t="n">
-        <v>1207</v>
+        <v>795</v>
       </c>
       <c r="P38" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -9896,26 +9756,26 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10 Jirang</t>
+          <t>3 Raliang</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>44173</v>
+        <v>42961</v>
       </c>
       <c r="F39" t="n">
-        <v>38734</v>
+        <v>40927</v>
       </c>
       <c r="G39" t="n">
-        <v>5439</v>
+        <v>2034</v>
       </c>
       <c r="N39" t="n">
-        <v>1306</v>
+        <v>1635</v>
       </c>
       <c r="O39" t="n">
-        <v>4038</v>
+        <v>361</v>
       </c>
       <c r="P39" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -9946,26 +9806,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>11 Umsning</t>
+          <t>4 Mowkaiaw</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>42386</v>
+        <v>42837</v>
       </c>
       <c r="F40" t="n">
-        <v>39105</v>
+        <v>40706</v>
       </c>
       <c r="G40" t="n">
-        <v>3281</v>
+        <v>2131</v>
       </c>
       <c r="N40" t="n">
-        <v>1459</v>
+        <v>1260</v>
       </c>
       <c r="O40" t="n">
-        <v>1667</v>
+        <v>774</v>
       </c>
       <c r="P40" t="n">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -9996,26 +9856,26 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12 Umroi</t>
+          <t>5 Sutnga Saipung</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>35372</v>
+        <v>51956</v>
       </c>
       <c r="F41" t="n">
-        <v>32739</v>
+        <v>48631</v>
       </c>
       <c r="G41" t="n">
-        <v>2633</v>
+        <v>3325</v>
       </c>
       <c r="N41" t="n">
-        <v>1200</v>
+        <v>1614</v>
       </c>
       <c r="O41" t="n">
-        <v>1335</v>
+        <v>1390</v>
       </c>
       <c r="P41" t="n">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -10046,26 +9906,26 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>13 Mawryngkneng</t>
+          <t>6 Khliehriat</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>43706</v>
+        <v>52461</v>
       </c>
       <c r="F42" t="n">
-        <v>40504</v>
+        <v>48160</v>
       </c>
       <c r="G42" t="n">
-        <v>3202</v>
+        <v>4301</v>
       </c>
       <c r="N42" t="n">
-        <v>1976</v>
+        <v>1984</v>
       </c>
       <c r="O42" t="n">
-        <v>1073</v>
+        <v>2058</v>
       </c>
       <c r="P42" t="n">
-        <v>153</v>
+        <v>259</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -10096,26 +9956,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>14 Pynthorumkhrah</t>
+          <t>7 Amlarem</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>36571</v>
+        <v>42124</v>
       </c>
       <c r="F43" t="n">
-        <v>29784</v>
+        <v>40650</v>
       </c>
       <c r="G43" t="n">
-        <v>6787</v>
+        <v>1474</v>
       </c>
       <c r="N43" t="n">
-        <v>1903</v>
+        <v>958</v>
       </c>
       <c r="O43" t="n">
-        <v>4758</v>
+        <v>499</v>
       </c>
       <c r="P43" t="n">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -10146,26 +10006,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>15 Mawlai</t>
+          <t>8 Mawhati</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>52893</v>
+        <v>42861</v>
       </c>
       <c r="F44" t="n">
-        <v>47323</v>
+        <v>40960</v>
       </c>
       <c r="G44" t="n">
-        <v>5570</v>
+        <v>1901</v>
       </c>
       <c r="N44" t="n">
-        <v>1775</v>
+        <v>1027</v>
       </c>
       <c r="O44" t="n">
-        <v>3672</v>
+        <v>793</v>
       </c>
       <c r="P44" t="n">
-        <v>123</v>
+        <v>81</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -10196,26 +10056,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16 East Shillong</t>
+          <t>9 Nongpoh</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>25300</v>
+        <v>40943</v>
       </c>
       <c r="F45" t="n">
-        <v>19692</v>
+        <v>38528</v>
       </c>
       <c r="G45" t="n">
-        <v>5608</v>
+        <v>2415</v>
       </c>
       <c r="N45" t="n">
-        <v>1419</v>
+        <v>1104</v>
       </c>
       <c r="O45" t="n">
-        <v>4134</v>
+        <v>1207</v>
       </c>
       <c r="P45" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -10246,26 +10106,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>17 North Shillong</t>
+          <t>10 Jirang</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>28072</v>
+        <v>44173</v>
       </c>
       <c r="F46" t="n">
-        <v>21509</v>
+        <v>38734</v>
       </c>
       <c r="G46" t="n">
-        <v>6563</v>
+        <v>5439</v>
       </c>
       <c r="N46" t="n">
-        <v>2011</v>
+        <v>1306</v>
       </c>
       <c r="O46" t="n">
-        <v>4423</v>
+        <v>4038</v>
       </c>
       <c r="P46" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -10296,26 +10156,26 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>18 West Shillong</t>
+          <t>11 Umsning</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>27331</v>
+        <v>42386</v>
       </c>
       <c r="F47" t="n">
-        <v>21182</v>
+        <v>39105</v>
       </c>
       <c r="G47" t="n">
-        <v>6149</v>
+        <v>3281</v>
       </c>
       <c r="N47" t="n">
-        <v>1820</v>
+        <v>1459</v>
       </c>
       <c r="O47" t="n">
-        <v>4269</v>
+        <v>1667</v>
       </c>
       <c r="P47" t="n">
-        <v>60</v>
+        <v>155</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -10346,26 +10206,26 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>19 South Shillong</t>
+          <t>12 Umroi</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>34077</v>
+        <v>35372</v>
       </c>
       <c r="F48" t="n">
-        <v>26322</v>
+        <v>32739</v>
       </c>
       <c r="G48" t="n">
-        <v>7755</v>
+        <v>2633</v>
       </c>
       <c r="N48" t="n">
-        <v>1809</v>
+        <v>1200</v>
       </c>
       <c r="O48" t="n">
-        <v>5901</v>
+        <v>1335</v>
       </c>
       <c r="P48" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -10396,26 +10256,26 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>20 Mylliem</t>
+          <t>13 Mawryngkneng</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>38922</v>
+        <v>43706</v>
       </c>
       <c r="F49" t="n">
-        <v>36289</v>
+        <v>40504</v>
       </c>
       <c r="G49" t="n">
-        <v>2633</v>
+        <v>3202</v>
       </c>
       <c r="N49" t="n">
-        <v>1260</v>
+        <v>1976</v>
       </c>
       <c r="O49" t="n">
-        <v>1282</v>
+        <v>1073</v>
       </c>
       <c r="P49" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -10446,26 +10306,26 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>21 Nongthymmai</t>
+          <t>14 Pynthorumkhrah</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>36850</v>
+        <v>36571</v>
       </c>
       <c r="F50" t="n">
-        <v>29437</v>
+        <v>29784</v>
       </c>
       <c r="G50" t="n">
-        <v>7413</v>
+        <v>6787</v>
       </c>
       <c r="N50" t="n">
-        <v>2068</v>
+        <v>1903</v>
       </c>
       <c r="O50" t="n">
-        <v>5213</v>
+        <v>4758</v>
       </c>
       <c r="P50" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -10496,26 +10356,26 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>22 Nongkrem</t>
+          <t>15 Mawlai</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>40276</v>
+        <v>52893</v>
       </c>
       <c r="F51" t="n">
-        <v>37246</v>
+        <v>47323</v>
       </c>
       <c r="G51" t="n">
-        <v>3030</v>
+        <v>5570</v>
       </c>
       <c r="N51" t="n">
-        <v>1341</v>
+        <v>1775</v>
       </c>
       <c r="O51" t="n">
-        <v>1622</v>
+        <v>3672</v>
       </c>
       <c r="P51" t="n">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -10546,26 +10406,26 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>23 Sohiong</t>
+          <t>16 East Shillong</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>37496</v>
+        <v>25300</v>
       </c>
       <c r="F52" t="n">
-        <v>35223</v>
+        <v>19692</v>
       </c>
       <c r="G52" t="n">
-        <v>2273</v>
+        <v>5608</v>
       </c>
       <c r="N52" t="n">
-        <v>1212</v>
+        <v>1419</v>
       </c>
       <c r="O52" t="n">
-        <v>968</v>
+        <v>4134</v>
       </c>
       <c r="P52" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -10596,26 +10456,26 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>24 Mawphlang</t>
+          <t>17 North Shillong</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>38518</v>
+        <v>28072</v>
       </c>
       <c r="F53" t="n">
-        <v>36168</v>
+        <v>21509</v>
       </c>
       <c r="G53" t="n">
-        <v>2350</v>
+        <v>6563</v>
       </c>
       <c r="N53" t="n">
-        <v>1507</v>
+        <v>2011</v>
       </c>
       <c r="O53" t="n">
-        <v>675</v>
+        <v>4423</v>
       </c>
       <c r="P53" t="n">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -10646,26 +10506,26 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>25 Mawsynram</t>
+          <t>18 West Shillong</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>39984</v>
+        <v>27331</v>
       </c>
       <c r="F54" t="n">
-        <v>37626</v>
+        <v>21182</v>
       </c>
       <c r="G54" t="n">
-        <v>2358</v>
+        <v>6149</v>
       </c>
       <c r="N54" t="n">
-        <v>1483</v>
+        <v>1820</v>
       </c>
       <c r="O54" t="n">
-        <v>739</v>
+        <v>4269</v>
       </c>
       <c r="P54" t="n">
-        <v>136</v>
+        <v>60</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -10696,26 +10556,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>26 Shella</t>
+          <t>19 South Shillong</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>37925</v>
+        <v>34077</v>
       </c>
       <c r="F55" t="n">
-        <v>35207</v>
+        <v>26322</v>
       </c>
       <c r="G55" t="n">
-        <v>2718</v>
+        <v>7755</v>
       </c>
       <c r="N55" t="n">
-        <v>1558</v>
+        <v>1809</v>
       </c>
       <c r="O55" t="n">
-        <v>1072</v>
+        <v>5901</v>
       </c>
       <c r="P55" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -10746,26 +10606,26 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>27 Pynursla</t>
+          <t>20 Mylliem</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>41748</v>
+        <v>38922</v>
       </c>
       <c r="F56" t="n">
-        <v>39314</v>
+        <v>36289</v>
       </c>
       <c r="G56" t="n">
-        <v>2434</v>
+        <v>2633</v>
       </c>
       <c r="N56" t="n">
-        <v>1941</v>
+        <v>1260</v>
       </c>
       <c r="O56" t="n">
-        <v>390</v>
+        <v>1282</v>
       </c>
       <c r="P56" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -10796,26 +10656,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>28 Sohra</t>
+          <t>21 Nongthymmai</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>32220</v>
+        <v>36850</v>
       </c>
       <c r="F57" t="n">
-        <v>30532</v>
+        <v>29437</v>
       </c>
       <c r="G57" t="n">
-        <v>1688</v>
+        <v>7413</v>
       </c>
       <c r="N57" t="n">
-        <v>1329</v>
+        <v>2068</v>
       </c>
       <c r="O57" t="n">
-        <v>313</v>
+        <v>5213</v>
       </c>
       <c r="P57" t="n">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -10846,26 +10706,26 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>29 Mawkynrew</t>
+          <t>22 Nongkrem</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>40257</v>
+        <v>40276</v>
       </c>
       <c r="F58" t="n">
-        <v>38802</v>
+        <v>37246</v>
       </c>
       <c r="G58" t="n">
-        <v>1455</v>
+        <v>3030</v>
       </c>
       <c r="N58" t="n">
-        <v>907</v>
+        <v>1341</v>
       </c>
       <c r="O58" t="n">
-        <v>436</v>
+        <v>1622</v>
       </c>
       <c r="P58" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -10896,26 +10756,26 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>30 Mairang</t>
+          <t>23 Sohiong</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>46252</v>
+        <v>37496</v>
       </c>
       <c r="F59" t="n">
-        <v>44814</v>
+        <v>35223</v>
       </c>
       <c r="G59" t="n">
-        <v>1438</v>
+        <v>2273</v>
       </c>
       <c r="N59" t="n">
-        <v>828</v>
+        <v>1212</v>
       </c>
       <c r="O59" t="n">
-        <v>520</v>
+        <v>968</v>
       </c>
       <c r="P59" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -10946,26 +10806,26 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>31 Mawthadraishan</t>
+          <t>24 Mawphlang</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>47498</v>
+        <v>38518</v>
       </c>
       <c r="F60" t="n">
-        <v>46333</v>
+        <v>36168</v>
       </c>
       <c r="G60" t="n">
-        <v>1165</v>
+        <v>2350</v>
       </c>
       <c r="N60" t="n">
-        <v>635</v>
+        <v>1507</v>
       </c>
       <c r="O60" t="n">
-        <v>468</v>
+        <v>675</v>
       </c>
       <c r="P60" t="n">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -10996,26 +10856,26 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>32 Nongstoin</t>
+          <t>25 Mawsynram</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>48244</v>
+        <v>39984</v>
       </c>
       <c r="F61" t="n">
-        <v>46649</v>
+        <v>37626</v>
       </c>
       <c r="G61" t="n">
-        <v>1595</v>
+        <v>2358</v>
       </c>
       <c r="N61" t="n">
-        <v>1075</v>
+        <v>1483</v>
       </c>
       <c r="O61" t="n">
-        <v>432</v>
+        <v>739</v>
       </c>
       <c r="P61" t="n">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -11046,26 +10906,26 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>33 Rambrai Jyrngam</t>
+          <t>26 Shella</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43962</v>
+        <v>37925</v>
       </c>
       <c r="F62" t="n">
-        <v>40903</v>
+        <v>35207</v>
       </c>
       <c r="G62" t="n">
-        <v>3059</v>
+        <v>2718</v>
       </c>
       <c r="N62" t="n">
-        <v>1519</v>
+        <v>1558</v>
       </c>
       <c r="O62" t="n">
-        <v>1310</v>
+        <v>1072</v>
       </c>
       <c r="P62" t="n">
-        <v>230</v>
+        <v>88</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -11096,26 +10956,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>34 Mawshynrut</t>
+          <t>27 Pynursla</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>45521</v>
+        <v>41748</v>
       </c>
       <c r="F63" t="n">
-        <v>42268</v>
+        <v>39314</v>
       </c>
       <c r="G63" t="n">
-        <v>3253</v>
+        <v>2434</v>
       </c>
       <c r="N63" t="n">
-        <v>1861</v>
+        <v>1941</v>
       </c>
       <c r="O63" t="n">
-        <v>1271</v>
+        <v>390</v>
       </c>
       <c r="P63" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -11146,26 +11006,26 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>35 Ranikor</t>
+          <t>28 Sohra</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>39247</v>
+        <v>32220</v>
       </c>
       <c r="F64" t="n">
-        <v>37254</v>
+        <v>30532</v>
       </c>
       <c r="G64" t="n">
-        <v>1993</v>
+        <v>1688</v>
       </c>
       <c r="N64" t="n">
-        <v>1216</v>
+        <v>1329</v>
       </c>
       <c r="O64" t="n">
-        <v>705</v>
+        <v>313</v>
       </c>
       <c r="P64" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -11196,26 +11056,26 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>36 Mawkyrwat</t>
+          <t>29 Mawkynrew</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>41345</v>
+        <v>40257</v>
       </c>
       <c r="F65" t="n">
-        <v>39870</v>
+        <v>38802</v>
       </c>
       <c r="G65" t="n">
-        <v>1475</v>
+        <v>1455</v>
       </c>
       <c r="N65" t="n">
-        <v>1089</v>
+        <v>907</v>
       </c>
       <c r="O65" t="n">
-        <v>312</v>
+        <v>436</v>
       </c>
       <c r="P65" t="n">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -11246,26 +11106,26 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>37 Kharkutta</t>
+          <t>30 Mairang</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>44866</v>
+        <v>46252</v>
       </c>
       <c r="F66" t="n">
-        <v>40784</v>
+        <v>44814</v>
       </c>
       <c r="G66" t="n">
-        <v>4082</v>
+        <v>1438</v>
       </c>
       <c r="N66" t="n">
-        <v>1050</v>
+        <v>828</v>
       </c>
       <c r="O66" t="n">
-        <v>2910</v>
+        <v>520</v>
       </c>
       <c r="P66" t="n">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -11296,26 +11156,26 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>38 Mendipathar</t>
+          <t>31 Mawthadraishan</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>31082</v>
+        <v>47498</v>
       </c>
       <c r="F67" t="n">
-        <v>28184</v>
+        <v>46333</v>
       </c>
       <c r="G67" t="n">
-        <v>2898</v>
+        <v>1165</v>
       </c>
       <c r="N67" t="n">
-        <v>1282</v>
+        <v>635</v>
       </c>
       <c r="O67" t="n">
-        <v>1524</v>
+        <v>468</v>
       </c>
       <c r="P67" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -11346,26 +11206,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>39 Resubelpara</t>
+          <t>32 Nongstoin</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>32138</v>
+        <v>48244</v>
       </c>
       <c r="F68" t="n">
-        <v>29834</v>
+        <v>46649</v>
       </c>
       <c r="G68" t="n">
-        <v>2304</v>
+        <v>1595</v>
       </c>
       <c r="N68" t="n">
-        <v>919</v>
+        <v>1075</v>
       </c>
       <c r="O68" t="n">
-        <v>1315</v>
+        <v>432</v>
       </c>
       <c r="P68" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -11396,26 +11256,26 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>40 Bajengdoba</t>
+          <t>33 Rambrai Jyrngam</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>35662</v>
+        <v>43962</v>
       </c>
       <c r="F69" t="n">
-        <v>33211</v>
+        <v>40903</v>
       </c>
       <c r="G69" t="n">
-        <v>2451</v>
+        <v>3059</v>
       </c>
       <c r="N69" t="n">
-        <v>1327</v>
+        <v>1519</v>
       </c>
       <c r="O69" t="n">
-        <v>1020</v>
+        <v>1310</v>
       </c>
       <c r="P69" t="n">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -11446,26 +11306,26 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>41 Songsak</t>
+          <t>34 Mawshynrut</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>35518</v>
+        <v>45521</v>
       </c>
       <c r="F70" t="n">
-        <v>33304</v>
+        <v>42268</v>
       </c>
       <c r="G70" t="n">
-        <v>2214</v>
+        <v>3253</v>
       </c>
       <c r="N70" t="n">
-        <v>1069</v>
+        <v>1861</v>
       </c>
       <c r="O70" t="n">
-        <v>1029</v>
+        <v>1271</v>
       </c>
       <c r="P70" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -11496,26 +11356,26 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>42 Rongjeng</t>
+          <t>35 Ranikor</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>39099</v>
+        <v>39247</v>
       </c>
       <c r="F71" t="n">
-        <v>36444</v>
+        <v>37254</v>
       </c>
       <c r="G71" t="n">
-        <v>2655</v>
+        <v>1993</v>
       </c>
       <c r="N71" t="n">
-        <v>1055</v>
+        <v>1216</v>
       </c>
       <c r="O71" t="n">
-        <v>1361</v>
+        <v>705</v>
       </c>
       <c r="P71" t="n">
-        <v>239</v>
+        <v>72</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -11546,26 +11406,26 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>43 William Nagar</t>
+          <t>36 Mawkyrwat</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>40150</v>
+        <v>41345</v>
       </c>
       <c r="F72" t="n">
-        <v>35764</v>
+        <v>39870</v>
       </c>
       <c r="G72" t="n">
-        <v>4386</v>
+        <v>1475</v>
       </c>
       <c r="N72" t="n">
-        <v>781</v>
+        <v>1089</v>
       </c>
       <c r="O72" t="n">
-        <v>3371</v>
+        <v>312</v>
       </c>
       <c r="P72" t="n">
-        <v>234</v>
+        <v>74</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -11596,26 +11456,26 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>44 Raksamgre</t>
+          <t>37 Kharkutta</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>33456</v>
+        <v>44866</v>
       </c>
       <c r="F73" t="n">
-        <v>30713</v>
+        <v>40784</v>
       </c>
       <c r="G73" t="n">
-        <v>2743</v>
+        <v>4082</v>
       </c>
       <c r="N73" t="n">
-        <v>1768</v>
+        <v>1050</v>
       </c>
       <c r="O73" t="n">
-        <v>878</v>
+        <v>2910</v>
       </c>
       <c r="P73" t="n">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -11646,26 +11506,26 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>45 Tikrikilla</t>
+          <t>38 Mendipathar</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>38102</v>
+        <v>31082</v>
       </c>
       <c r="F74" t="n">
-        <v>35614</v>
+        <v>28184</v>
       </c>
       <c r="G74" t="n">
-        <v>2488</v>
+        <v>2898</v>
       </c>
       <c r="N74" t="n">
-        <v>1611</v>
+        <v>1282</v>
       </c>
       <c r="O74" t="n">
-        <v>813</v>
+        <v>1524</v>
       </c>
       <c r="P74" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -11696,26 +11556,26 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>46 Phulbari</t>
+          <t>39 Resubelpara</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>35902</v>
+        <v>32138</v>
       </c>
       <c r="F75" t="n">
-        <v>33941</v>
+        <v>29834</v>
       </c>
       <c r="G75" t="n">
-        <v>1961</v>
+        <v>2304</v>
       </c>
       <c r="N75" t="n">
-        <v>1256</v>
+        <v>919</v>
       </c>
       <c r="O75" t="n">
-        <v>653</v>
+        <v>1315</v>
       </c>
       <c r="P75" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -11746,26 +11606,26 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>47 Rajabala</t>
+          <t>40 Bajengdoba</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>38778</v>
+        <v>35662</v>
       </c>
       <c r="F76" t="n">
-        <v>37092</v>
+        <v>33211</v>
       </c>
       <c r="G76" t="n">
-        <v>1686</v>
+        <v>2451</v>
       </c>
       <c r="N76" t="n">
-        <v>926</v>
+        <v>1327</v>
       </c>
       <c r="O76" t="n">
-        <v>659</v>
+        <v>1020</v>
       </c>
       <c r="P76" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -11796,26 +11656,26 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>48 Selsella</t>
+          <t>41 Songsak</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>39293</v>
+        <v>35518</v>
       </c>
       <c r="F77" t="n">
-        <v>37294</v>
+        <v>33304</v>
       </c>
       <c r="G77" t="n">
-        <v>1999</v>
+        <v>2214</v>
       </c>
       <c r="N77" t="n">
-        <v>1200</v>
+        <v>1069</v>
       </c>
       <c r="O77" t="n">
-        <v>726</v>
+        <v>1029</v>
       </c>
       <c r="P77" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
@@ -11846,26 +11706,26 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>49 Dadenggre</t>
+          <t>42 Rongjeng</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>39880</v>
+        <v>39099</v>
       </c>
       <c r="F78" t="n">
-        <v>37073</v>
+        <v>36444</v>
       </c>
       <c r="G78" t="n">
-        <v>2807</v>
+        <v>2655</v>
       </c>
       <c r="N78" t="n">
-        <v>1870</v>
+        <v>1055</v>
       </c>
       <c r="O78" t="n">
-        <v>851</v>
+        <v>1361</v>
       </c>
       <c r="P78" t="n">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -11896,26 +11756,26 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>50 North Tura</t>
+          <t>43 William Nagar</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>36631</v>
+        <v>40150</v>
       </c>
       <c r="F79" t="n">
-        <v>32415</v>
+        <v>35764</v>
       </c>
       <c r="G79" t="n">
-        <v>4216</v>
+        <v>4386</v>
       </c>
       <c r="N79" t="n">
-        <v>1526</v>
+        <v>781</v>
       </c>
       <c r="O79" t="n">
-        <v>2579</v>
+        <v>3371</v>
       </c>
       <c r="P79" t="n">
-        <v>111</v>
+        <v>234</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
@@ -11946,26 +11806,26 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>51 South Tura</t>
+          <t>44 Raksamgre</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>35796</v>
+        <v>33456</v>
       </c>
       <c r="F80" t="n">
-        <v>30784</v>
+        <v>30713</v>
       </c>
       <c r="G80" t="n">
-        <v>5012</v>
+        <v>2743</v>
       </c>
       <c r="N80" t="n">
-        <v>1938</v>
+        <v>1768</v>
       </c>
       <c r="O80" t="n">
-        <v>3009</v>
+        <v>878</v>
       </c>
       <c r="P80" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
@@ -11996,26 +11856,26 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>52 Rangsakona</t>
+          <t>45 Tikrikilla</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>40914</v>
+        <v>38102</v>
       </c>
       <c r="F81" t="n">
-        <v>37742</v>
+        <v>35614</v>
       </c>
       <c r="G81" t="n">
-        <v>3172</v>
+        <v>2488</v>
       </c>
       <c r="N81" t="n">
-        <v>1747</v>
+        <v>1611</v>
       </c>
       <c r="O81" t="n">
-        <v>1327</v>
+        <v>813</v>
       </c>
       <c r="P81" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
@@ -12046,26 +11906,26 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>53 Ampati</t>
+          <t>46 Phulbari</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>35573</v>
+        <v>35902</v>
       </c>
       <c r="F82" t="n">
-        <v>34326</v>
+        <v>33941</v>
       </c>
       <c r="G82" t="n">
-        <v>1247</v>
+        <v>1961</v>
       </c>
       <c r="N82" t="n">
-        <v>755</v>
+        <v>1256</v>
       </c>
       <c r="O82" t="n">
-        <v>406</v>
+        <v>653</v>
       </c>
       <c r="P82" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
@@ -12096,26 +11956,26 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>54 Mahendraganj</t>
+          <t>47 Rajabala</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>39339</v>
+        <v>38778</v>
       </c>
       <c r="F83" t="n">
-        <v>37887</v>
+        <v>37092</v>
       </c>
       <c r="G83" t="n">
-        <v>1452</v>
+        <v>1686</v>
       </c>
       <c r="N83" t="n">
-        <v>812</v>
+        <v>926</v>
       </c>
       <c r="O83" t="n">
-        <v>582</v>
+        <v>659</v>
       </c>
       <c r="P83" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
@@ -12146,26 +12006,26 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>55 Salmanpara</t>
+          <t>48 Selsella</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>33971</v>
+        <v>39293</v>
       </c>
       <c r="F84" t="n">
-        <v>32458</v>
+        <v>37294</v>
       </c>
       <c r="G84" t="n">
-        <v>1513</v>
+        <v>1999</v>
       </c>
       <c r="N84" t="n">
-        <v>911</v>
+        <v>1200</v>
       </c>
       <c r="O84" t="n">
-        <v>440</v>
+        <v>726</v>
       </c>
       <c r="P84" t="n">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -12196,26 +12056,26 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>56 Gambegre</t>
+          <t>49 Dadenggre</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>34857</v>
+        <v>39880</v>
       </c>
       <c r="F85" t="n">
-        <v>33072</v>
+        <v>37073</v>
       </c>
       <c r="G85" t="n">
-        <v>1785</v>
+        <v>2807</v>
       </c>
       <c r="N85" t="n">
-        <v>899</v>
+        <v>1870</v>
       </c>
       <c r="O85" t="n">
-        <v>716</v>
+        <v>851</v>
       </c>
       <c r="P85" t="n">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -12246,26 +12106,26 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>57 Dalu</t>
+          <t>50 North Tura</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23305</v>
+        <v>36631</v>
       </c>
       <c r="F86" t="n">
-        <v>21642</v>
+        <v>32415</v>
       </c>
       <c r="G86" t="n">
-        <v>1663</v>
+        <v>4216</v>
       </c>
       <c r="N86" t="n">
-        <v>872</v>
+        <v>1526</v>
       </c>
       <c r="O86" t="n">
-        <v>663</v>
+        <v>2579</v>
       </c>
       <c r="P86" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
@@ -12296,26 +12156,26 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>58 Rongara Siju</t>
+          <t>51 South Tura</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>38179</v>
+        <v>35796</v>
       </c>
       <c r="F87" t="n">
-        <v>34882</v>
+        <v>30784</v>
       </c>
       <c r="G87" t="n">
-        <v>3297</v>
+        <v>5012</v>
       </c>
       <c r="N87" t="n">
-        <v>1261</v>
+        <v>1938</v>
       </c>
       <c r="O87" t="n">
-        <v>1798</v>
+        <v>3009</v>
       </c>
       <c r="P87" t="n">
-        <v>238</v>
+        <v>65</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
@@ -12346,26 +12206,26 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>59 Chokpot</t>
+          <t>52 Rangsakona</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>35921</v>
+        <v>40914</v>
       </c>
       <c r="F88" t="n">
-        <v>33400</v>
+        <v>37742</v>
       </c>
       <c r="G88" t="n">
-        <v>2521</v>
+        <v>3172</v>
       </c>
       <c r="N88" t="n">
-        <v>1270</v>
+        <v>1747</v>
       </c>
       <c r="O88" t="n">
-        <v>1151</v>
+        <v>1327</v>
       </c>
       <c r="P88" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
@@ -12396,38 +12256,388 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>53 Ampati</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>35573</v>
+      </c>
+      <c r="F89" t="n">
+        <v>34326</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1247</v>
+      </c>
+      <c r="N89" t="n">
+        <v>755</v>
+      </c>
+      <c r="O89" t="n">
+        <v>406</v>
+      </c>
+      <c r="P89" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>54 Mahendraganj</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>39339</v>
+      </c>
+      <c r="F90" t="n">
+        <v>37887</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1452</v>
+      </c>
+      <c r="N90" t="n">
+        <v>812</v>
+      </c>
+      <c r="O90" t="n">
+        <v>582</v>
+      </c>
+      <c r="P90" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>55 Salmanpara</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>33971</v>
+      </c>
+      <c r="F91" t="n">
+        <v>32458</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1513</v>
+      </c>
+      <c r="N91" t="n">
+        <v>911</v>
+      </c>
+      <c r="O91" t="n">
+        <v>440</v>
+      </c>
+      <c r="P91" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>56 Gambegre</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>34857</v>
+      </c>
+      <c r="F92" t="n">
+        <v>33072</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1785</v>
+      </c>
+      <c r="N92" t="n">
+        <v>899</v>
+      </c>
+      <c r="O92" t="n">
+        <v>716</v>
+      </c>
+      <c r="P92" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>57 Dalu</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>23305</v>
+      </c>
+      <c r="F93" t="n">
+        <v>21642</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1663</v>
+      </c>
+      <c r="N93" t="n">
+        <v>872</v>
+      </c>
+      <c r="O93" t="n">
+        <v>663</v>
+      </c>
+      <c r="P93" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>58 Rongara Siju</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>38179</v>
+      </c>
+      <c r="F94" t="n">
+        <v>34882</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3297</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1261</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1798</v>
+      </c>
+      <c r="P94" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>59 Chokpot</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>35921</v>
+      </c>
+      <c r="F95" t="n">
+        <v>33400</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2521</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1270</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1151</v>
+      </c>
+      <c r="P95" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>constituencies</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ac</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>60 Baghmara</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="E96" t="n">
         <v>36388</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F96" t="n">
         <v>34367</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G96" t="n">
         <v>2021</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N96" t="n">
         <v>1052</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O96" t="n">
         <v>833</v>
       </c>
-      <c r="P89" t="n">
+      <c r="P96" t="n">
         <v>136</v>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>Election Department, Government of Meghalaya (Chief Electoral Officer), press note No. EL.63/2026/29 of 5 August 2026 with the SIR status report by constituency</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
         <is>
           <t>no</t>
         </is>
